--- a/survey_templates/035_moodboard_creation_survey--survey_templates.xlsx
+++ b/survey_templates/035_moodboard_creation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_image</t>
+          <t>target_audience</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Project Image</t>
+          <t>Target Audience</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>inspiration_sources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Target Audience</t>
+          <t>Inspiration Sources</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -653,46 +653,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inspiration_sources</t>
+          <t>preferred_color</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inspiration Sources</t>
+          <t>Preferred Color</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>preferred_color</t>
+          <t>moodboard_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Preferred Color</t>
+          <t>Moodboard Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>moodboard_name</t>
+          <t>project_url</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moodboard Name</t>
+          <t>Project URL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,361 +727,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_url</t>
+          <t>project_image</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project URL</t>
+          <t>Project Image</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_url_url</t>
+          <t>target_age_group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project URL</t>
+          <t>Target Age Group</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>project_image</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Project Image</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>target_age_group</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Target Age Group</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>design_style</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Design Style</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>project_color_scheme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Project Color Scheme</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>preferred_color</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Preferred Color</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>target_audience</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Target Audience</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>design_style</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Design Style</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>project_image</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Project Image</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>project_url</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Project URL</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_url_url</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Project URL</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_image</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Project Image</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>target_audience</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Target Audience</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>inspiration_sources</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Inspiration Sources</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>preferred_color</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Preferred Color</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +776,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1392,397 +1070,6 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>Children</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>modern</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Modern</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>minimalist</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Minimalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>vintage</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Vintage</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>project_color_scheme_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>project_color_scheme_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>project_color_scheme_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>project_color_scheme_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>men</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Men</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Women</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>children</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Children</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>modern</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Modern</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>minimalist</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Minimalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>design_style_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>vintage</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Vintage</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>men</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Men</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Women</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>children</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Children</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yellow</t>
         </is>
       </c>
     </row>
